--- a/Team-Data/2013-14/12-30-2013-14.xlsx
+++ b/Team-Data/2013-14/12-30-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,10 +806,10 @@
         <v>1.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>11</v>
@@ -769,7 +836,7 @@
         <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO2" t="n">
         <v>19</v>
@@ -778,7 +845,7 @@
         <v>20</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR2" t="n">
         <v>29</v>
@@ -799,19 +866,19 @@
         <v>10</v>
       </c>
       <c r="AX2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA2" t="n">
         <v>23</v>
       </c>
-      <c r="AY2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>24</v>
-      </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
         <v>11</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-1.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF3" t="n">
         <v>18</v>
       </c>
-      <c r="AF3" t="n">
-        <v>17</v>
-      </c>
       <c r="AG3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>27</v>
@@ -954,10 +1021,10 @@
         <v>15</v>
       </c>
       <c r="AO3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP3" t="n">
         <v>28</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>27</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
@@ -966,7 +1033,7 @@
         <v>23</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>24</v>
@@ -981,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-5.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1118,7 +1185,7 @@
         <v>10</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>29</v>
@@ -1133,7 +1200,7 @@
         <v>21</v>
       </c>
       <c r="AN4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>5</v>
@@ -1142,7 +1209,7 @@
         <v>4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
         <v>25</v>
@@ -1166,7 +1233,7 @@
         <v>27</v>
       </c>
       <c r="AY4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ4" t="n">
         <v>25</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>0.438</v>
+        <v>0.452</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="J5" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.421</v>
+        <v>0.422</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>15.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q5" t="n">
         <v>0.719</v>
@@ -1255,43 +1322,43 @@
         <v>33</v>
       </c>
       <c r="T5" t="n">
-        <v>43.7</v>
+        <v>43.6</v>
       </c>
       <c r="U5" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="V5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W5" t="n">
         <v>6.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>92.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>-1.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>17</v>
@@ -1300,25 +1367,25 @@
         <v>14</v>
       </c>
       <c r="AI5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK5" t="n">
         <v>29</v>
       </c>
       <c r="AL5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
         <v>29</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP5" t="n">
         <v>7</v>
@@ -1330,7 +1397,7 @@
         <v>19</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>12</v>
@@ -1345,19 +1412,19 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>17</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1389,91 +1456,91 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
-        <v>0.414</v>
+        <v>0.393</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>34</v>
+        <v>34.2</v>
       </c>
       <c r="J6" t="n">
-        <v>80.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.425</v>
+        <v>0.424</v>
       </c>
       <c r="L6" t="n">
         <v>5.5</v>
       </c>
       <c r="M6" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.329</v>
+        <v>0.326</v>
       </c>
       <c r="O6" t="n">
-        <v>18.2</v>
+        <v>17.7</v>
       </c>
       <c r="P6" t="n">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
-        <v>32.7</v>
+        <v>32.8</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6</v>
+        <v>44.9</v>
       </c>
       <c r="U6" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V6" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W6" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="X6" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y6" t="n">
         <v>6.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>91.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.4</v>
+        <v>-1.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG6" t="n">
         <v>22</v>
@@ -1497,22 +1564,22 @@
         <v>28</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
         <v>8</v>
@@ -1527,16 +1594,16 @@
         <v>28</v>
       </c>
       <c r="AX6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB6" t="n">
         <v>30</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
@@ -1688,7 +1755,7 @@
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
@@ -1709,10 +1776,10 @@
         <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AY7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ7" t="n">
         <v>4</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" t="n">
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.581</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
@@ -1780,37 +1847,37 @@
         <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="O8" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="P8" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U8" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="X8" t="n">
         <v>4.7</v>
@@ -1822,16 +1889,16 @@
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.8</v>
+        <v>103.9</v>
       </c>
       <c r="AC8" t="n">
         <v>1.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1855,19 +1922,19 @@
         <v>5</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
@@ -1876,13 +1943,13 @@
         <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
         <v>27</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>9</v>
@@ -1891,10 +1958,10 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1903,7 +1970,7 @@
         <v>28</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>12</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" t="n">
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G9" t="n">
-        <v>0.467</v>
+        <v>0.483</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
@@ -1953,10 +2020,10 @@
         <v>37.1</v>
       </c>
       <c r="J9" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L9" t="n">
         <v>7.3</v>
@@ -1965,64 +2032,64 @@
         <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.728</v>
+        <v>0.725</v>
       </c>
       <c r="R9" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S9" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="U9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V9" t="n">
         <v>15.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z9" t="n">
         <v>21.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="AC9" t="n">
         <v>-1</v>
       </c>
       <c r="AD9" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2031,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK9" t="n">
         <v>21</v>
@@ -2043,22 +2110,22 @@
         <v>15</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
         <v>5</v>
@@ -2076,16 +2143,16 @@
         <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ9" t="n">
         <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G10" t="n">
-        <v>0.424</v>
+        <v>0.438</v>
       </c>
       <c r="H10" t="n">
         <v>48.5</v>
       </c>
       <c r="I10" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="J10" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.45</v>
@@ -2150,25 +2217,25 @@
         <v>0.321</v>
       </c>
       <c r="O10" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P10" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.665</v>
+        <v>0.668</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T10" t="n">
         <v>44.3</v>
       </c>
       <c r="U10" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V10" t="n">
         <v>15.5</v>
@@ -2177,37 +2244,37 @@
         <v>8.9</v>
       </c>
       <c r="X10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.4</v>
+        <v>20.2</v>
       </c>
       <c r="AB10" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>13</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>10</v>
@@ -2216,19 +2283,19 @@
         <v>6</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM10" t="n">
         <v>23</v>
       </c>
       <c r="AN10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2246,28 +2313,28 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AW10" t="n">
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>13</v>
       </c>
       <c r="AZ10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,16 +2456,16 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
         <v>4</v>
@@ -2416,10 +2483,10 @@
         <v>19</v>
       </c>
       <c r="AQ11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,7 +2495,7 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV11" t="n">
         <v>29</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -2559,19 +2626,19 @@
         <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>6</v>
       </c>
       <c r="AF12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG12" t="n">
         <v>7</v>
       </c>
-      <c r="AG12" t="n">
-        <v>6</v>
-      </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>15</v>
@@ -2592,7 +2659,7 @@
         <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2616,7 +2683,7 @@
         <v>28</v>
       </c>
       <c r="AW12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
         <v>3</v>
@@ -2625,7 +2692,7 @@
         <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>9.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2774,10 +2841,10 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
         <v>5</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -2845,97 +2912,97 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
         <v>21</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>0.636</v>
+        <v>0.656</v>
       </c>
       <c r="H14" t="n">
         <v>48.5</v>
       </c>
       <c r="I14" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J14" t="n">
-        <v>82.3</v>
+        <v>82.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.461</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
         <v>7.8</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.333</v>
+        <v>0.332</v>
       </c>
       <c r="O14" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="Q14" t="n">
         <v>0.72</v>
       </c>
       <c r="R14" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
         <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X14" t="n">
         <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
         <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.5</v>
+        <v>105</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>13</v>
@@ -2965,25 +3032,25 @@
         <v>26</v>
       </c>
       <c r="AR14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>8</v>
       </c>
-      <c r="AV14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>11</v>
-      </c>
       <c r="AX14" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3105,13 +3172,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG15" t="n">
         <v>21</v>
@@ -3132,7 +3199,7 @@
         <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN15" t="n">
         <v>11</v>
@@ -3141,13 +3208,13 @@
         <v>16</v>
       </c>
       <c r="AP15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS15" t="n">
         <v>11</v>
@@ -3171,13 +3238,13 @@
         <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
       </c>
       <c r="BB15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3209,43 +3276,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G16" t="n">
-        <v>0.433</v>
+        <v>0.448</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J16" t="n">
-        <v>82.3</v>
+        <v>82.5</v>
       </c>
       <c r="K16" t="n">
         <v>0.449</v>
       </c>
       <c r="L16" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.349</v>
       </c>
       <c r="O16" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="P16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="Q16" t="n">
         <v>0.756</v>
@@ -3254,43 +3321,43 @@
         <v>12</v>
       </c>
       <c r="S16" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.4</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
         <v>21.4</v>
       </c>
       <c r="V16" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="W16" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA16" t="n">
         <v>19.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-2.6</v>
+        <v>-2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF16" t="n">
         <v>17</v>
@@ -3302,40 +3369,40 @@
         <v>19</v>
       </c>
       <c r="AI16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM16" t="n">
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP16" t="n">
         <v>25</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AQ16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS16" t="n">
         <v>24</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>25</v>
-      </c>
       <c r="AT16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
@@ -3344,22 +3411,22 @@
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX16" t="n">
         <v>28</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA16" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB16" t="n">
         <v>25</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>26</v>
       </c>
       <c r="BC16" t="n">
         <v>21</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3391,55 +3458,55 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F17" t="n">
         <v>7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.774</v>
+        <v>0.767</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
       </c>
       <c r="I17" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J17" t="n">
-        <v>76.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.511</v>
       </c>
       <c r="L17" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>21.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="O17" t="n">
         <v>17.8</v>
       </c>
       <c r="P17" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.753</v>
+        <v>0.757</v>
       </c>
       <c r="R17" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="S17" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T17" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="U17" t="n">
         <v>24.1</v>
@@ -3448,43 +3515,43 @@
         <v>15.3</v>
       </c>
       <c r="W17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="X17" t="n">
         <v>4.8</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="AA17" t="n">
         <v>20.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>104.5</v>
+        <v>104.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AD17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3499,16 +3566,16 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3529,16 +3596,16 @@
         <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
         <v>6</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3666,7 +3733,7 @@
         <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ18" t="n">
         <v>19</v>
@@ -3687,7 +3754,7 @@
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ18" t="n">
         <v>7</v>
@@ -3699,7 +3766,7 @@
         <v>26</v>
       </c>
       <c r="AT18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>18</v>
@@ -3711,7 +3778,7 @@
         <v>24</v>
       </c>
       <c r="AX18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY18" t="n">
         <v>18</v>
@@ -3723,11 +3790,11 @@
         <v>16</v>
       </c>
       <c r="BB18" t="n">
+        <v>29</v>
+      </c>
+      <c r="BC18" t="n">
         <v>28</v>
       </c>
-      <c r="BC18" t="n">
-        <v>29</v>
-      </c>
       <c r="BD18" t="n">
         <v>10</v>
       </c>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19" t="n">
         <v>15</v>
       </c>
       <c r="F19" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" t="n">
-        <v>0.484</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.3</v>
       </c>
       <c r="I19" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J19" t="n">
-        <v>89.3</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="K19" t="n">
         <v>0.429</v>
@@ -3785,22 +3852,22 @@
         <v>23.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.336</v>
+        <v>0.338</v>
       </c>
       <c r="O19" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R19" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="S19" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T19" t="n">
         <v>46.2</v>
@@ -3809,10 +3876,10 @@
         <v>23.4</v>
       </c>
       <c r="V19" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>2.9</v>
@@ -3824,28 +3891,28 @@
         <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.2</v>
+        <v>106.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>12</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI19" t="n">
         <v>11</v>
@@ -3866,7 +3933,7 @@
         <v>25</v>
       </c>
       <c r="AO19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3881,13 +3948,13 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -3937,106 +4004,106 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" t="n">
         <v>15</v>
       </c>
       <c r="G20" t="n">
-        <v>0.483</v>
+        <v>0.464</v>
       </c>
       <c r="H20" t="n">
         <v>48.7</v>
       </c>
       <c r="I20" t="n">
-        <v>39.6</v>
+        <v>39.3</v>
       </c>
       <c r="J20" t="n">
         <v>87.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.452</v>
+        <v>0.449</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="M20" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.386</v>
+        <v>0.391</v>
       </c>
       <c r="O20" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P20" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="S20" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="T20" t="n">
+        <v>44</v>
+      </c>
+      <c r="U20" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="V20" t="n">
         <v>13.4</v>
       </c>
-      <c r="S20" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>23</v>
-      </c>
-      <c r="V20" t="n">
-        <v>13.2</v>
-      </c>
       <c r="W20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>7</v>
       </c>
       <c r="AI20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
         <v>24</v>
@@ -4051,7 +4118,7 @@
         <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4060,13 +4127,13 @@
         <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4075,16 +4142,16 @@
         <v>5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ20" t="n">
         <v>23</v>
       </c>
       <c r="BA20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -4197,10 +4264,10 @@
         <v>-4.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF21" t="n">
         <v>27</v>
@@ -4254,13 +4321,13 @@
         <v>1</v>
       </c>
       <c r="AW21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ21" t="n">
         <v>29</v>
@@ -4269,7 +4336,7 @@
         <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>25</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>8.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
         <v>7</v>
@@ -4415,7 +4482,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ22" t="n">
         <v>2</v>
@@ -4439,7 +4506,7 @@
         <v>13</v>
       </c>
       <c r="AX22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
@@ -4576,13 +4643,13 @@
         <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>16</v>
@@ -4597,10 +4664,10 @@
         <v>24</v>
       </c>
       <c r="AP23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
@@ -4624,13 +4691,13 @@
         <v>25</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ23" t="n">
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB23" t="n">
         <v>21</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -4743,10 +4810,10 @@
         <v>-8.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF24" t="n">
         <v>27</v>
@@ -4758,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
         <v>2</v>
@@ -4773,7 +4840,7 @@
         <v>10</v>
       </c>
       <c r="AN24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO24" t="n">
         <v>20</v>
@@ -4794,7 +4861,7 @@
         <v>6</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4812,7 +4879,7 @@
         <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -4847,22 +4914,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F25" t="n">
         <v>11</v>
       </c>
       <c r="G25" t="n">
-        <v>0.633</v>
+        <v>0.621</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J25" t="n">
         <v>83</v>
@@ -4871,64 +4938,64 @@
         <v>0.461</v>
       </c>
       <c r="L25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="M25" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="N25" t="n">
         <v>0.373</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P25" t="n">
         <v>23.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.743</v>
+        <v>0.748</v>
       </c>
       <c r="R25" t="n">
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T25" t="n">
         <v>43.3</v>
       </c>
       <c r="U25" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="V25" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="W25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>103.7</v>
+        <v>103.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AE25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>6</v>
@@ -4937,7 +5004,7 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
         <v>12</v>
@@ -4946,7 +5013,7 @@
         <v>18</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4955,19 +5022,19 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO25" t="n">
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
         <v>21</v>
       </c>
       <c r="AR25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4976,16 +5043,16 @@
         <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV25" t="n">
         <v>26</v>
       </c>
       <c r="AW25" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
         <v>7</v>
@@ -4994,10 +5061,10 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5029,22 +5096,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="n">
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>0.774</v>
+        <v>0.8</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="J26" t="n">
         <v>87.40000000000001</v>
@@ -5056,46 +5123,46 @@
         <v>10.3</v>
       </c>
       <c r="M26" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.403</v>
+        <v>0.404</v>
       </c>
       <c r="O26" t="n">
         <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.819</v>
+        <v>0.821</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>33</v>
+        <v>33.2</v>
       </c>
       <c r="T26" t="n">
-        <v>46</v>
+        <v>46.2</v>
       </c>
       <c r="U26" t="n">
         <v>24</v>
       </c>
       <c r="V26" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W26" t="n">
         <v>5.7</v>
       </c>
       <c r="X26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA26" t="n">
         <v>20.5</v>
@@ -5104,10 +5171,10 @@
         <v>108.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AD26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>2</v>
@@ -5119,13 +5186,13 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>2</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>11</v>
@@ -5134,16 +5201,16 @@
         <v>1</v>
       </c>
       <c r="AM26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN26" t="n">
         <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5155,22 +5222,22 @@
         <v>8</v>
       </c>
       <c r="AT26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>4</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>-3.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
@@ -5337,7 +5404,7 @@
         <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU27" t="n">
         <v>20</v>
@@ -5352,7 +5419,7 @@
         <v>29</v>
       </c>
       <c r="AY27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5471,16 +5538,16 @@
         <v>7.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
       </c>
       <c r="AF28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
         <v>27</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5519,7 +5586,7 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>2</v>
@@ -5531,7 +5598,7 @@
         <v>14</v>
       </c>
       <c r="AX28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY28" t="n">
         <v>16</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>0.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF29" t="n">
         <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
         <v>5</v>
@@ -5689,7 +5756,7 @@
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
         <v>6</v>
@@ -5704,7 +5771,7 @@
         <v>15</v>
       </c>
       <c r="AU29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>0.294</v>
+        <v>0.273</v>
       </c>
       <c r="H30" t="n">
         <v>48.3</v>
@@ -5781,64 +5848,64 @@
         <v>0.431</v>
       </c>
       <c r="L30" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M30" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.347</v>
+        <v>0.346</v>
       </c>
       <c r="O30" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="P30" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R30" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S30" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T30" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V30" t="n">
         <v>15.5</v>
       </c>
       <c r="W30" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>92.7</v>
+        <v>93</v>
       </c>
       <c r="AC30" t="n">
-        <v>-8.1</v>
+        <v>-8.5</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AF30" t="n">
         <v>29</v>
@@ -5859,19 +5926,19 @@
         <v>24</v>
       </c>
       <c r="AL30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AM30" t="n">
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AQ30" t="n">
         <v>14</v>
@@ -5883,13 +5950,13 @@
         <v>29</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV30" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>22</v>
@@ -5904,13 +5971,13 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
@@ -5939,58 +6006,58 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F31" t="n">
         <v>14</v>
       </c>
       <c r="G31" t="n">
-        <v>0.5</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
         <v>49.1</v>
       </c>
       <c r="I31" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J31" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L31" t="n">
         <v>8.5</v>
       </c>
       <c r="M31" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="N31" t="n">
-        <v>0.394</v>
+        <v>0.395</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R31" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S31" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T31" t="n">
         <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V31" t="n">
         <v>15.6</v>
@@ -5999,34 +6066,34 @@
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>99.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="AD31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AF31" t="n">
         <v>11</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="n">
         <v>4</v>
@@ -6038,10 +6105,10 @@
         <v>11</v>
       </c>
       <c r="AK31" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM31" t="n">
         <v>14</v>
@@ -6050,46 +6117,46 @@
         <v>4</v>
       </c>
       <c r="AO31" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AP31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT31" t="n">
         <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
         <v>22</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX31" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA31" t="n">
         <v>24</v>
       </c>
-      <c r="AY31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>23</v>
-      </c>
       <c r="BB31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-30-2013-14</t>
+          <t>2013-12-30</t>
         </is>
       </c>
     </row>
